--- a/output/pdf_financials_xlsx/TRIP.xlsx
+++ b/output/pdf_financials_xlsx/TRIP.xlsx
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.208847</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.53118</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-5.641118</v>
+        <v>-5.849965</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.654596</v>
+        <v>-8.185776000000001</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-5.011077</v>
+        <v>-5.219924</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-6.723389</v>
+        <v>-7.254569</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -957,10 +957,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-126.8734047705794</v>
+        <v>-132.1611163675317</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-141.4860244601146</v>
+        <v>-152.6640994566266</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -2457,13 +2457,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.164163</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.220133</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.136482</v>
       </c>
     </row>
     <row r="125">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.164163</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.220133</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.136482</v>
       </c>
     </row>
     <row r="126">
@@ -6160,7 +6160,11 @@
           <t>Lease payments (Note 12)</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -7239,7 +7243,11 @@
           <t>Lease payments (Note 13)</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E146" s="5" t="n">
         <v>-0.164163</v>
       </c>
@@ -9310,7 +9318,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E215" s="5" t="n">
@@ -9736,7 +9744,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E229" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRIP.xlsx
+++ b/output/pdf_financials_xlsx/TRIP.xlsx
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="B114" s="3" t="n">
-        <v>0</v>
+        <v>-0.199996</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>0.147593</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.010544</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -5879,7 +5879,11 @@
           <t>Proceeds from disposal of marketable securities (Note 4)</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>-</t>
@@ -6933,7 +6937,11 @@
           <t>Proceeds from sale of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E136" s="5" t="n">
         <v>0.147593</v>
       </c>
@@ -6962,7 +6970,11 @@
           <t>Purchase of marketable securities (Note 5)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>-0.199996</v>
       </c>
